--- a/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0195.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/story_dialogue/lang_multi_text/lang_multi_text__story_dialogue__part_0195.xlsx
@@ -31579,7 +31579,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Ta có mùi gì lạ không...?</t>
+          <t>Tao có mùi gì lạ không...?</t>
         </is>
       </c>
     </row>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Bạn đang làm gì ở đây?</t>
+          <t>Cậu làm gì ở đây vậy?</t>
         </is>
       </c>
     </row>
@@ -32684,7 +32684,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>À, &lt;ano=Taiping Musical&gt;múa lân&lt;/ano&gt; là một truyền thống ở Kim Châu mà.</t>
+          <t>À, &lt;ano=Taiping Musical&gt;múa lân&lt;/ano&gt; là một truyền thống ở Jinzhou mà.</t>
         </is>
       </c>
     </row>
@@ -32814,7 +32814,7 @@
       </c>
       <c r="M498" t="inlineStr">
         <is>
-          <t>Jinzhou có rất nhiều hoạt động thú vị. Ta nóng lòng muốn dẫn ngươi đi khám phá quá!</t>
+          <t>Jinzhou có rất nhiều hoạt động thú vị. Tao nóng lòng muốn dẫn mày đi khám phá quá!</t>
         </is>
       </c>
     </row>
